--- a/doc/Time scenarios_V4.xlsx
+++ b/doc/Time scenarios_V4.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30408"/>
-  <workbookPr/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
+  <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://ritesoftware1-my.sharepoint.com/personal/gayathri_radhakrishnan_rite_digital/Documents/Documents/1. O2C/5. Time/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://ritesoftware1-my.sharepoint.com/personal/sampaul_jeevan_rite_digital/Documents/O2C/Time Module/VBS/O2C_TIME_V2/doc/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{D9F31618-E860-447C-ACD1-0DF624F2AA55}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="36" documentId="8_{D9F31618-E860-447C-ACD1-0DF624F2AA55}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{48BC4BAA-4AD5-45A5-9D62-80F39557439A}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="3" activeTab="3" xr2:uid="{78D12D0A-26E9-4982-B350-7CFB003AA1BE}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" firstSheet="3" activeTab="3" xr2:uid="{78D12D0A-26E9-4982-B350-7CFB003AA1BE}"/>
   </bookViews>
   <sheets>
     <sheet name="Statuses" sheetId="5" state="hidden" r:id="rId1"/>
@@ -748,7 +748,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="10">
+  <fonts count="10" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1625,13 +1625,13 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{43BA99B2-06F1-4FEE-ACD5-5C0ED0C9E9E1}">
   <dimension ref="A1:C11"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="42.7109375" customWidth="1"/>
     <col min="2" max="2" width="21.140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="27" t="s">
         <v>0</v>
       </c>
@@ -1642,7 +1642,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" ht="25.5">
+    <row r="2" spans="1:3" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A2" s="28" t="s">
         <v>3</v>
       </c>
@@ -1653,7 +1653,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="3" spans="1:3" ht="25.5">
+    <row r="3" spans="1:3" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A3" s="29" t="s">
         <v>6</v>
       </c>
@@ -1664,7 +1664,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="4" spans="1:3" ht="38.25">
+    <row r="4" spans="1:3" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A4" s="29" t="s">
         <v>9</v>
       </c>
@@ -1675,7 +1675,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="5" spans="1:3" ht="25.5">
+    <row r="5" spans="1:3" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A5" s="30" t="s">
         <v>12</v>
       </c>
@@ -1686,7 +1686,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="7" spans="1:3">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" s="27" t="s">
         <v>0</v>
       </c>
@@ -1697,7 +1697,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="8" spans="1:3">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" s="28" t="s">
         <v>15</v>
       </c>
@@ -1708,7 +1708,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="9" spans="1:3">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" s="29" t="s">
         <v>17</v>
       </c>
@@ -1719,7 +1719,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="10" spans="1:3" ht="38.25">
+    <row r="10" spans="1:3" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A10" s="29" t="s">
         <v>20</v>
       </c>
@@ -1730,7 +1730,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="11" spans="1:3" ht="38.25">
+    <row r="11" spans="1:3" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A11" s="30" t="s">
         <v>22</v>
       </c>
@@ -1749,19 +1749,19 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B53E0FB3-6225-4D63-A69A-FCA3639C4FE4}">
   <dimension ref="A1:G8"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="18.42578125" customWidth="1"/>
     <col min="3" max="3" width="57.5703125" customWidth="1"/>
     <col min="7" max="7" width="44.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="G1" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="3" spans="1:7">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3" s="35" t="s">
         <v>25</v>
       </c>
@@ -1772,7 +1772,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:7">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4" s="34" t="s">
         <v>27</v>
       </c>
@@ -1783,7 +1783,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="5" spans="1:7" ht="25.5">
+    <row r="5" spans="1:7" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A5" s="34" t="s">
         <v>27</v>
       </c>
@@ -1794,7 +1794,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="6" spans="1:7" ht="25.5">
+    <row r="6" spans="1:7" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A6" s="34" t="s">
         <v>27</v>
       </c>
@@ -1805,7 +1805,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="7" spans="1:7" ht="25.5">
+    <row r="7" spans="1:7" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A7" s="34" t="s">
         <v>27</v>
       </c>
@@ -1816,7 +1816,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="8" spans="1:7" ht="25.5">
+    <row r="8" spans="1:7" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A8" s="34" t="s">
         <v>27</v>
       </c>
@@ -1835,7 +1835,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{ADA22E1A-14BC-4295-9975-B9A362B6BCE0}">
   <dimension ref="A1:Q31"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="64.85546875" style="3" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="14" style="3" customWidth="1"/>
@@ -1851,7 +1851,7 @@
     <col min="15" max="15" width="30.85546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17">
+    <row r="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
         <v>33</v>
       </c>
@@ -1872,7 +1872,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="2" spans="1:17">
+    <row r="2" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>1</v>
       </c>
@@ -1889,12 +1889,12 @@
         <v>42</v>
       </c>
     </row>
-    <row r="3" spans="1:17">
+    <row r="3" spans="1:17" x14ac:dyDescent="0.25">
       <c r="B3" s="3" t="s">
         <v>43</v>
       </c>
     </row>
-    <row r="4" spans="1:17">
+    <row r="4" spans="1:17" x14ac:dyDescent="0.25">
       <c r="B4" s="36" t="s">
         <v>44</v>
       </c>
@@ -1906,7 +1906,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="5" spans="1:17">
+    <row r="5" spans="1:17" x14ac:dyDescent="0.25">
       <c r="B5" s="36" t="s">
         <v>47</v>
       </c>
@@ -1945,7 +1945,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="6" spans="1:17">
+    <row r="6" spans="1:17" x14ac:dyDescent="0.25">
       <c r="B6" s="36" t="s">
         <v>55</v>
       </c>
@@ -1959,7 +1959,7 @@
       <c r="P6" s="38"/>
       <c r="Q6" s="38"/>
     </row>
-    <row r="7" spans="1:17">
+    <row r="7" spans="1:17" x14ac:dyDescent="0.25">
       <c r="B7" s="37" t="s">
         <v>58</v>
       </c>
@@ -1976,7 +1976,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="8" spans="1:17">
+    <row r="8" spans="1:17" x14ac:dyDescent="0.25">
       <c r="B8" s="40" t="s">
         <v>62</v>
       </c>
@@ -1994,7 +1994,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="9" spans="1:17">
+    <row r="9" spans="1:17" x14ac:dyDescent="0.25">
       <c r="B9" s="40" t="s">
         <v>63</v>
       </c>
@@ -2012,7 +2012,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="10" spans="1:17">
+    <row r="10" spans="1:17" x14ac:dyDescent="0.25">
       <c r="B10" s="37" t="s">
         <v>64</v>
       </c>
@@ -2035,7 +2035,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="11" spans="1:17">
+    <row r="11" spans="1:17" x14ac:dyDescent="0.25">
       <c r="B11" s="36" t="s">
         <v>68</v>
       </c>
@@ -2049,19 +2049,19 @@
         <v>70</v>
       </c>
     </row>
-    <row r="12" spans="1:17">
+    <row r="12" spans="1:17" x14ac:dyDescent="0.25">
       <c r="B12" s="36"/>
       <c r="C12" s="36"/>
       <c r="O12" t="s">
         <v>71</v>
       </c>
     </row>
-    <row r="13" spans="1:17">
+    <row r="13" spans="1:17" x14ac:dyDescent="0.25">
       <c r="O13" t="s">
         <v>72</v>
       </c>
     </row>
-    <row r="14" spans="1:17">
+    <row r="14" spans="1:17" x14ac:dyDescent="0.25">
       <c r="B14" s="3" t="s">
         <v>73</v>
       </c>
@@ -2069,7 +2069,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="15" spans="1:17">
+    <row r="15" spans="1:17" x14ac:dyDescent="0.25">
       <c r="B15" s="36" t="s">
         <v>75</v>
       </c>
@@ -2084,11 +2084,11 @@
         <v>42</v>
       </c>
     </row>
-    <row r="16" spans="1:17">
+    <row r="16" spans="1:17" x14ac:dyDescent="0.25">
       <c r="B16" s="36"/>
       <c r="C16" s="36"/>
     </row>
-    <row r="17" spans="1:15">
+    <row r="17" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A17">
         <v>3</v>
       </c>
@@ -2111,7 +2111,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="18" spans="1:15">
+    <row r="18" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A18">
         <v>4</v>
       </c>
@@ -2134,7 +2134,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="19" spans="1:15">
+    <row r="19" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A19">
         <v>5</v>
       </c>
@@ -2157,7 +2157,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="20" spans="1:15" ht="30">
+    <row r="20" spans="1:15" ht="30" x14ac:dyDescent="0.25">
       <c r="A20">
         <v>6</v>
       </c>
@@ -2180,7 +2180,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="21" spans="1:15">
+    <row r="21" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A21">
         <v>7</v>
       </c>
@@ -2200,7 +2200,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="22" spans="1:15" ht="30">
+    <row r="22" spans="1:15" ht="30" x14ac:dyDescent="0.25">
       <c r="A22">
         <v>8</v>
       </c>
@@ -2217,7 +2217,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="23" spans="1:15" ht="30">
+    <row r="23" spans="1:15" ht="30" x14ac:dyDescent="0.25">
       <c r="A23">
         <v>9</v>
       </c>
@@ -2240,7 +2240,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="24" spans="1:15">
+    <row r="24" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A24">
         <v>10</v>
       </c>
@@ -2266,7 +2266,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="25" spans="1:15">
+    <row r="25" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A25">
         <v>11</v>
       </c>
@@ -2292,7 +2292,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="26" spans="1:15">
+    <row r="26" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A26">
         <v>12</v>
       </c>
@@ -2315,7 +2315,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="27" spans="1:15" ht="30">
+    <row r="27" spans="1:15" ht="30" x14ac:dyDescent="0.25">
       <c r="A27">
         <v>13</v>
       </c>
@@ -2338,7 +2338,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="28" spans="1:15">
+    <row r="28" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A28">
         <v>14</v>
       </c>
@@ -2358,7 +2358,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="29" spans="1:15">
+    <row r="29" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A29">
         <v>15</v>
       </c>
@@ -2375,7 +2375,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="30" spans="1:15" ht="30">
+    <row r="30" spans="1:15" ht="30" x14ac:dyDescent="0.25">
       <c r="A30">
         <v>16</v>
       </c>
@@ -2393,7 +2393,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="31" spans="1:15" ht="30">
+    <row r="31" spans="1:15" ht="30" x14ac:dyDescent="0.25">
       <c r="A31">
         <v>17</v>
       </c>
@@ -2421,12 +2421,12 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B56EF768-B2BC-4BEE-B8BB-60DF9C3EEE54}">
   <dimension ref="A1:O56"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="9.140625" style="42"/>
     <col min="2" max="2" width="20.7109375" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="19.28515625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="64.85546875" style="3" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="64.85546875" style="3" customWidth="1"/>
     <col min="5" max="5" width="16" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="16.5703125" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="17.85546875" bestFit="1" customWidth="1"/>
@@ -2440,7 +2440,7 @@
     <col min="15" max="15" width="6.28515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1" s="41" t="s">
         <v>33</v>
       </c>
@@ -2466,7 +2466,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="2" spans="1:8">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" s="42">
         <v>1</v>
       </c>
@@ -2486,7 +2486,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="3" spans="1:8">
+    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3" s="42">
         <v>2</v>
       </c>
@@ -2494,7 +2494,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="4" spans="1:8">
+    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A4" s="42">
         <v>2.1</v>
       </c>
@@ -2502,7 +2502,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="5" spans="1:8">
+    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A5" s="42" t="s">
         <v>115</v>
       </c>
@@ -2522,7 +2522,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="6" spans="1:8">
+    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A6" s="42" t="s">
         <v>117</v>
       </c>
@@ -2542,7 +2542,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="7" spans="1:8" ht="17.25" customHeight="1">
+    <row r="7" spans="1:8" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="42">
         <v>2.2000000000000002</v>
       </c>
@@ -2554,7 +2554,7 @@
       <c r="F7" s="44"/>
       <c r="G7" s="44"/>
     </row>
-    <row r="8" spans="1:8">
+    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A8" s="42" t="s">
         <v>120</v>
       </c>
@@ -2574,7 +2574,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="9" spans="1:8">
+    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A9" s="42" t="s">
         <v>122</v>
       </c>
@@ -2594,7 +2594,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="10" spans="1:8">
+    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A10" s="42" t="s">
         <v>124</v>
       </c>
@@ -2614,7 +2614,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="11" spans="1:8">
+    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
       <c r="C11" s="15"/>
       <c r="D11" s="47" t="s">
         <v>126</v>
@@ -2629,7 +2629,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="12" spans="1:8">
+    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A12" s="42" t="s">
         <v>128</v>
       </c>
@@ -2649,7 +2649,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="13" spans="1:8">
+    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A13" s="42" t="s">
         <v>130</v>
       </c>
@@ -2669,7 +2669,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="14" spans="1:8">
+    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A14" s="42" t="s">
         <v>132</v>
       </c>
@@ -2689,7 +2689,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="15" spans="1:8">
+    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
       <c r="C15" s="15"/>
       <c r="D15" s="47" t="s">
         <v>126</v>
@@ -2707,7 +2707,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="16" spans="1:8" ht="30">
+    <row r="16" spans="1:8" ht="30" x14ac:dyDescent="0.25">
       <c r="A16" s="42">
         <v>2.2999999999999998</v>
       </c>
@@ -2717,7 +2717,7 @@
       </c>
       <c r="G16" s="14"/>
     </row>
-    <row r="17" spans="1:15" ht="30">
+    <row r="17" spans="1:15" ht="30" x14ac:dyDescent="0.25">
       <c r="A17" s="42" t="s">
         <v>135</v>
       </c>
@@ -2737,7 +2737,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="18" spans="1:15">
+    <row r="18" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A18" s="42" t="s">
         <v>137</v>
       </c>
@@ -2760,7 +2760,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="19" spans="1:15">
+    <row r="19" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A19" s="42" t="s">
         <v>138</v>
       </c>
@@ -2780,7 +2780,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="20" spans="1:15">
+    <row r="20" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A20" s="42" t="s">
         <v>139</v>
       </c>
@@ -2800,7 +2800,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="21" spans="1:15">
+    <row r="21" spans="1:15" x14ac:dyDescent="0.25">
       <c r="C21" s="15"/>
       <c r="D21" s="47" t="s">
         <v>126</v>
@@ -2815,7 +2815,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="22" spans="1:15" ht="30">
+    <row r="22" spans="1:15" ht="30" x14ac:dyDescent="0.25">
       <c r="A22" s="42" t="s">
         <v>141</v>
       </c>
@@ -2835,7 +2835,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="23" spans="1:15">
+    <row r="23" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A23" s="42" t="s">
         <v>143</v>
       </c>
@@ -2858,7 +2858,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="24" spans="1:15">
+    <row r="24" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A24" s="42" t="s">
         <v>144</v>
       </c>
@@ -2878,7 +2878,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="25" spans="1:15">
+    <row r="25" spans="1:15" x14ac:dyDescent="0.25">
       <c r="C25" s="15"/>
       <c r="D25" s="47" t="s">
         <v>126</v>
@@ -2896,7 +2896,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="26" spans="1:15" ht="30">
+    <row r="26" spans="1:15" ht="30" x14ac:dyDescent="0.25">
       <c r="A26" s="42">
         <v>2.4</v>
       </c>
@@ -2927,7 +2927,7 @@
         <v>152</v>
       </c>
     </row>
-    <row r="27" spans="1:15">
+    <row r="27" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A27" s="42" t="s">
         <v>153</v>
       </c>
@@ -2953,7 +2953,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="28" spans="1:15">
+    <row r="28" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A28" s="42" t="s">
         <v>155</v>
       </c>
@@ -2979,7 +2979,7 @@
         <v>156</v>
       </c>
     </row>
-    <row r="29" spans="1:15">
+    <row r="29" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A29" s="42" t="s">
         <v>157</v>
       </c>
@@ -2999,7 +2999,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="30" spans="1:15">
+    <row r="30" spans="1:15" x14ac:dyDescent="0.25">
       <c r="B30" s="15"/>
       <c r="C30" s="15"/>
       <c r="D30" s="47" t="s">
@@ -3015,7 +3015,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="31" spans="1:15">
+    <row r="31" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A31" s="42" t="s">
         <v>158</v>
       </c>
@@ -3038,7 +3038,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="32" spans="1:15">
+    <row r="32" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A32" s="42" t="s">
         <v>159</v>
       </c>
@@ -3061,7 +3061,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="33" spans="1:8">
+    <row r="33" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A33" s="42" t="s">
         <v>160</v>
       </c>
@@ -3081,7 +3081,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="34" spans="1:8">
+    <row r="34" spans="1:8" x14ac:dyDescent="0.25">
       <c r="B34" s="15"/>
       <c r="C34" s="15"/>
       <c r="D34" s="47" t="s">
@@ -3100,7 +3100,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="35" spans="1:8">
+    <row r="35" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A35" s="42">
         <v>3</v>
       </c>
@@ -3111,7 +3111,7 @@
       </c>
       <c r="G35" s="15"/>
     </row>
-    <row r="36" spans="1:8">
+    <row r="36" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A36" s="42">
         <v>3.1</v>
       </c>
@@ -3131,13 +3131,13 @@
         <v>40</v>
       </c>
     </row>
-    <row r="37" spans="1:8">
+    <row r="37" spans="1:8" x14ac:dyDescent="0.25">
       <c r="B37" s="15"/>
       <c r="C37" s="15"/>
       <c r="D37" s="37"/>
       <c r="G37" s="15"/>
     </row>
-    <row r="38" spans="1:8">
+    <row r="38" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A38" s="42">
         <v>4</v>
       </c>
@@ -3157,7 +3157,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="39" spans="1:8">
+    <row r="39" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A39" s="42">
         <v>5</v>
       </c>
@@ -3175,7 +3175,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="40" spans="1:8">
+    <row r="40" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A40" s="42">
         <v>6</v>
       </c>
@@ -3193,7 +3193,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="41" spans="1:8">
+    <row r="41" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A41" s="42">
         <v>7</v>
       </c>
@@ -3219,7 +3219,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="42" spans="1:8" ht="30">
+    <row r="42" spans="1:8" ht="30" x14ac:dyDescent="0.25">
       <c r="A42" s="42">
         <v>8</v>
       </c>
@@ -3238,7 +3238,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="43" spans="1:8">
+    <row r="43" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A43" s="42">
         <v>9</v>
       </c>
@@ -3257,7 +3257,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="44" spans="1:8" ht="30">
+    <row r="44" spans="1:8" ht="30" x14ac:dyDescent="0.25">
       <c r="A44" s="42">
         <v>10</v>
       </c>
@@ -3276,7 +3276,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="45" spans="1:8" ht="30">
+    <row r="45" spans="1:8" ht="30" x14ac:dyDescent="0.25">
       <c r="A45" s="42">
         <v>11</v>
       </c>
@@ -3295,7 +3295,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="46" spans="1:8">
+    <row r="46" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A46" s="42">
         <v>12</v>
       </c>
@@ -3318,7 +3318,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="47" spans="1:8">
+    <row r="47" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A47" s="42">
         <v>13</v>
       </c>
@@ -3337,7 +3337,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="48" spans="1:8" ht="30">
+    <row r="48" spans="1:8" ht="30" x14ac:dyDescent="0.25">
       <c r="A48" s="42">
         <v>14</v>
       </c>
@@ -3356,7 +3356,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="49" spans="1:15">
+    <row r="49" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A49" s="42">
         <v>15</v>
       </c>
@@ -3373,7 +3373,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="50" spans="1:15">
+    <row r="50" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A50" s="42">
         <v>16</v>
       </c>
@@ -3390,7 +3390,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="51" spans="1:15" ht="30">
+    <row r="51" spans="1:15" ht="30" x14ac:dyDescent="0.25">
       <c r="A51" s="42">
         <v>17</v>
       </c>
@@ -3425,7 +3425,7 @@
         <v>152</v>
       </c>
     </row>
-    <row r="52" spans="1:15">
+    <row r="52" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A52" s="42">
         <v>18</v>
       </c>
@@ -3445,17 +3445,17 @@
         <v>40</v>
       </c>
     </row>
-    <row r="54" spans="1:15">
+    <row r="54" spans="1:15" x14ac:dyDescent="0.25">
       <c r="D54" s="4" t="s">
         <v>171</v>
       </c>
     </row>
-    <row r="55" spans="1:15" ht="45">
+    <row r="55" spans="1:15" ht="45" x14ac:dyDescent="0.25">
       <c r="D55" s="4" t="s">
         <v>172</v>
       </c>
     </row>
-    <row r="56" spans="1:15">
+    <row r="56" spans="1:15" x14ac:dyDescent="0.25">
       <c r="D56" s="4" t="s">
         <v>173</v>
       </c>
@@ -3469,14 +3469,14 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1AA30310-F8DD-4986-95E1-835049F65FFD}">
   <dimension ref="A4:J33"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="39.85546875" style="3" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="41" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="58" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="4" spans="2:10">
+    <row r="4" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B4" s="39" t="s">
         <v>48</v>
       </c>
@@ -3505,7 +3505,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="5" spans="2:10">
+    <row r="5" spans="2:10" x14ac:dyDescent="0.25">
       <c r="G5" s="38" t="s">
         <v>174</v>
       </c>
@@ -3515,7 +3515,7 @@
       <c r="I5" s="38"/>
       <c r="J5" s="38"/>
     </row>
-    <row r="6" spans="2:10">
+    <row r="6" spans="2:10" x14ac:dyDescent="0.25">
       <c r="G6" t="s">
         <v>60</v>
       </c>
@@ -3523,7 +3523,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="7" spans="2:10">
+    <row r="7" spans="2:10" x14ac:dyDescent="0.25">
       <c r="G7" t="s">
         <v>176</v>
       </c>
@@ -3531,7 +3531,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="8" spans="2:10">
+    <row r="8" spans="2:10" x14ac:dyDescent="0.25">
       <c r="G8" t="s">
         <v>178</v>
       </c>
@@ -3539,17 +3539,17 @@
         <v>178</v>
       </c>
     </row>
-    <row r="9" spans="2:10">
+    <row r="9" spans="2:10" x14ac:dyDescent="0.25">
       <c r="H9" t="s">
         <v>72</v>
       </c>
     </row>
-    <row r="10" spans="2:10">
+    <row r="10" spans="2:10" x14ac:dyDescent="0.25">
       <c r="H10" t="s">
         <v>74</v>
       </c>
     </row>
-    <row r="16" spans="2:10">
+    <row r="16" spans="2:10" x14ac:dyDescent="0.25">
       <c r="G16" s="38" t="s">
         <v>179</v>
       </c>
@@ -3557,7 +3557,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="17" spans="1:10">
+    <row r="17" spans="1:10" x14ac:dyDescent="0.25">
       <c r="G17" t="s">
         <v>181</v>
       </c>
@@ -3565,7 +3565,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="18" spans="1:10">
+    <row r="18" spans="1:10" x14ac:dyDescent="0.25">
       <c r="G18" t="s">
         <v>83</v>
       </c>
@@ -3573,7 +3573,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="19" spans="1:10">
+    <row r="19" spans="1:10" x14ac:dyDescent="0.25">
       <c r="G19" t="s">
         <v>182</v>
       </c>
@@ -3581,12 +3581,12 @@
         <v>87</v>
       </c>
     </row>
-    <row r="20" spans="1:10">
+    <row r="20" spans="1:10" x14ac:dyDescent="0.25">
       <c r="H20" t="s">
         <v>89</v>
       </c>
     </row>
-    <row r="22" spans="1:10">
+    <row r="22" spans="1:10" x14ac:dyDescent="0.25">
       <c r="G22" s="2" t="s">
         <v>93</v>
       </c>
@@ -3594,7 +3594,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="23" spans="1:10">
+    <row r="23" spans="1:10" x14ac:dyDescent="0.25">
       <c r="G23" t="s">
         <v>4</v>
       </c>
@@ -3602,7 +3602,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="24" spans="1:10">
+    <row r="24" spans="1:10" x14ac:dyDescent="0.25">
       <c r="G24" t="s">
         <v>7</v>
       </c>
@@ -3610,12 +3610,12 @@
         <v>98</v>
       </c>
     </row>
-    <row r="25" spans="1:10">
+    <row r="25" spans="1:10" x14ac:dyDescent="0.25">
       <c r="G25" t="s">
         <v>100</v>
       </c>
     </row>
-    <row r="26" spans="1:10">
+    <row r="26" spans="1:10" x14ac:dyDescent="0.25">
       <c r="G26" t="s">
         <v>103</v>
       </c>
@@ -3623,12 +3623,12 @@
         <v>10</v>
       </c>
     </row>
-    <row r="27" spans="1:10">
+    <row r="27" spans="1:10" x14ac:dyDescent="0.25">
       <c r="G27" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="30" spans="1:10">
+    <row r="30" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B30">
         <v>28</v>
       </c>
@@ -3657,7 +3657,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="31" spans="1:10">
+    <row r="31" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B31" s="39" t="s">
         <v>48</v>
       </c>
@@ -3686,7 +3686,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="32" spans="1:10" ht="45">
+    <row r="32" spans="1:10" ht="45" x14ac:dyDescent="0.25">
       <c r="A32" s="3" t="s">
         <v>183</v>
       </c>
@@ -3694,7 +3694,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="33" spans="7:7">
+    <row r="33" spans="7:7" x14ac:dyDescent="0.25">
       <c r="G33" t="s">
         <v>185</v>
       </c>
@@ -3707,42 +3707,42 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2158C4E5-A633-4121-9555-A513E46F539C}">
   <dimension ref="A1:B12"/>
-  <sheetFormatPr defaultColWidth="74.85546875" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="74.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:2" ht="29.25">
+    <row r="1" spans="1:2" ht="30" x14ac:dyDescent="0.25">
       <c r="A1" s="4" t="s">
         <v>186</v>
       </c>
     </row>
-    <row r="2" spans="1:2" ht="29.25">
+    <row r="2" spans="1:2" ht="30" x14ac:dyDescent="0.25">
       <c r="A2" s="48" t="s">
         <v>187</v>
       </c>
     </row>
-    <row r="3" spans="1:2" ht="43.5">
+    <row r="3" spans="1:2" ht="45" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
         <v>188</v>
       </c>
     </row>
-    <row r="4" spans="1:2" ht="29.25">
+    <row r="4" spans="1:2" ht="30" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
         <v>189</v>
       </c>
     </row>
-    <row r="5" spans="1:2" ht="29.25">
+    <row r="5" spans="1:2" ht="30" x14ac:dyDescent="0.25">
       <c r="A5" s="3" t="s">
         <v>190</v>
       </c>
     </row>
-    <row r="6" spans="1:2">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
         <v>191</v>
       </c>
     </row>
-    <row r="7" spans="1:2">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" s="3"/>
     </row>
-    <row r="8" spans="1:2" ht="29.25">
+    <row r="8" spans="1:2" ht="45" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
         <v>192</v>
       </c>
@@ -3750,20 +3750,20 @@
         <v>193</v>
       </c>
     </row>
-    <row r="9" spans="1:2" ht="57.75">
+    <row r="9" spans="1:2" ht="60" x14ac:dyDescent="0.25">
       <c r="A9" s="3" t="s">
         <v>194</v>
       </c>
     </row>
-    <row r="10" spans="1:2">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" s="3"/>
     </row>
-    <row r="11" spans="1:2">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" s="3" t="s">
         <v>195</v>
       </c>
     </row>
-    <row r="12" spans="1:2">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12" s="3" t="s">
         <v>196</v>
       </c>
@@ -3776,7 +3776,7 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1FFB2C79-DD50-49AB-9038-23FD1E3ABCB6}">
   <dimension ref="A1:H14"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="7.85546875" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="62.85546875" customWidth="1"/>
@@ -3788,7 +3788,7 @@
     <col min="8" max="8" width="14" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="C1" s="52" t="s">
         <v>197</v>
       </c>
@@ -3798,7 +3798,7 @@
       </c>
       <c r="F1" s="55"/>
     </row>
-    <row r="2" spans="1:8">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
         <v>33</v>
       </c>
@@ -3824,7 +3824,7 @@
         <v>201</v>
       </c>
     </row>
-    <row r="3" spans="1:8">
+    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>1</v>
       </c>
@@ -3848,7 +3848,7 @@
       </c>
       <c r="H3" s="12"/>
     </row>
-    <row r="4" spans="1:8">
+    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A4">
         <v>2</v>
       </c>
@@ -3874,7 +3874,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:8">
+    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A5">
         <v>3</v>
       </c>
@@ -3900,7 +3900,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="1:8">
+    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A6">
         <v>4</v>
       </c>
@@ -3924,7 +3924,7 @@
       </c>
       <c r="H6" s="12"/>
     </row>
-    <row r="7" spans="1:8">
+    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A7">
         <v>5</v>
       </c>
@@ -3950,7 +3950,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="8" spans="1:8">
+    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A8">
         <v>6</v>
       </c>
@@ -3976,7 +3976,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="9" spans="1:8">
+    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A9">
         <v>7</v>
       </c>
@@ -4000,7 +4000,7 @@
       </c>
       <c r="H9" s="12"/>
     </row>
-    <row r="10" spans="1:8">
+    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A10">
         <v>8</v>
       </c>
@@ -4026,7 +4026,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="11" spans="1:8">
+    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A11">
         <v>9</v>
       </c>
@@ -4052,7 +4052,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="12" spans="1:8">
+    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A12">
         <v>10</v>
       </c>
@@ -4076,7 +4076,7 @@
       </c>
       <c r="H12" s="12"/>
     </row>
-    <row r="13" spans="1:8">
+    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A13">
         <v>11</v>
       </c>
@@ -4102,7 +4102,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="14" spans="1:8">
+    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A14">
         <v>12</v>
       </c>
@@ -4139,21 +4139,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100141825638AF68E48BE51BAB791418D9F" ma:contentTypeVersion="7" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="cb2a48e8efacfd6d2a503d2c1d55a2ae">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="36b65478-844c-4614-a56e-bc6723dfd221" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="dbd7509555245dc45d0bdd6e8c6523b7" ns2:_="">
     <xsd:import namespace="36b65478-844c-4614-a56e-bc6723dfd221"/>
@@ -4315,14 +4300,52 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{62606E0A-B248-4E31-95A9-B842BC2421AB}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{72905B0D-C55A-43FF-BD7A-D1670C4FE435}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="36b65478-844c-4614-a56e-bc6723dfd221"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7BA170CA-5179-4619-BDDE-98607142C55C}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7BA170CA-5179-4619-BDDE-98607142C55C}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{72905B0D-C55A-43FF-BD7A-D1670C4FE435}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{62606E0A-B248-4E31-95A9-B842BC2421AB}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>